--- a/public/results/2025/Week 7 Skins.xlsx
+++ b/public/results/2025/Week 7 Skins.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amentumcms-my.sharepoint.com/personal/mark_hutter_amentumcms_com/Documents/DATA/Code/golf-league-site/public/results/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{DBBB26E3-A62B-4C64-B177-E34D2F1A43A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2B13333-B91D-4FF6-9D2D-4B3E75BAA5FE}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{DBBB26E3-A62B-4C64-B177-E34D2F1A43A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EAD785F-3944-4B43-BE06-68E9C61988DB}"/>
   <bookViews>
-    <workbookView xWindow="6435" yWindow="495" windowWidth="26730" windowHeight="18000" xr2:uid="{F705A57A-943D-4C93-A0B0-17476496A7BD}"/>
+    <workbookView xWindow="43470" yWindow="3600" windowWidth="26730" windowHeight="18000" xr2:uid="{F705A57A-943D-4C93-A0B0-17476496A7BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 7 Skins" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>Skins ($40) $4.44/hole</t>
   </si>
@@ -59,30 +59,6 @@
     <t>Handicap</t>
   </si>
   <si>
-    <t>Young, Mark (13)</t>
-  </si>
-  <si>
-    <t>Adkison, Tony (13)</t>
-  </si>
-  <si>
-    <t>Miller, Ryan (8)</t>
-  </si>
-  <si>
-    <t>Wise, Randy (15)</t>
-  </si>
-  <si>
-    <t>Morgan, Luke (10)</t>
-  </si>
-  <si>
-    <t>Hutter, Mark (8)</t>
-  </si>
-  <si>
-    <t>Ige, Shayne (22)</t>
-  </si>
-  <si>
-    <t>Bess, John (15)</t>
-  </si>
-  <si>
     <t>&lt;carry&gt;</t>
   </si>
   <si>
@@ -92,22 +68,49 @@
     <t>Ige (2)</t>
   </si>
   <si>
-    <t>Adkison (.5)</t>
-  </si>
-  <si>
     <t>Miller (.5)</t>
   </si>
   <si>
     <t>Young (1)</t>
   </si>
   <si>
-    <t>Adkison (1.5)</t>
-  </si>
-  <si>
     <t>Morgan (.5)</t>
   </si>
   <si>
     <t>Wise (.5)</t>
+  </si>
+  <si>
+    <t>Mark Y</t>
+  </si>
+  <si>
+    <t>Ton A</t>
+  </si>
+  <si>
+    <t>Ryan M</t>
+  </si>
+  <si>
+    <t>Randy W</t>
+  </si>
+  <si>
+    <t>Luke M</t>
+  </si>
+  <si>
+    <t>Mark H</t>
+  </si>
+  <si>
+    <t>Shayne I</t>
+  </si>
+  <si>
+    <t>John B</t>
+  </si>
+  <si>
+    <t>HDCP</t>
+  </si>
+  <si>
+    <t>Tony (1.5)</t>
+  </si>
+  <si>
+    <t>Tony (.5)</t>
   </si>
 </sst>
 </file>
@@ -117,7 +120,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,6 +167,19 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -541,14 +557,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -561,16 +571,10 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -582,16 +586,10 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -600,20 +598,11 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -630,17 +619,11 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -666,7 +649,6 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -676,11 +658,56 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -698,6 +725,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1020,1234 +1051,1237 @@
   <dimension ref="A1:O31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="8.28515625" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" customWidth="1"/>
-    <col min="6" max="6" width="8.140625" customWidth="1"/>
-    <col min="7" max="7" width="7.28515625" customWidth="1"/>
-    <col min="8" max="9" width="12.5703125" customWidth="1"/>
-    <col min="10" max="11" width="10.7109375" customWidth="1"/>
-    <col min="12" max="12" width="5.5703125" customWidth="1"/>
-    <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="8.7109375" customWidth="1"/>
-    <col min="15" max="15" width="7.42578125" customWidth="1"/>
+    <col min="1" max="2" width="9.140625" style="44"/>
+    <col min="3" max="11" width="8.7109375" style="44" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" style="44" customWidth="1"/>
+    <col min="13" max="13" width="5.85546875" style="44" customWidth="1"/>
+    <col min="14" max="15" width="6.5703125" style="44" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="44"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:15" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="5"/>
-      <c r="O1" s="6" t="s">
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="3"/>
+      <c r="O1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="8">
-        <v>1</v>
-      </c>
-      <c r="D2" s="8">
-        <v>2</v>
-      </c>
-      <c r="E2" s="8">
-        <v>3</v>
-      </c>
-      <c r="F2" s="8">
-        <v>4</v>
-      </c>
-      <c r="G2" s="8">
-        <v>5</v>
-      </c>
-      <c r="H2" s="8">
-        <v>6</v>
-      </c>
-      <c r="I2" s="8">
+      <c r="A2" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="5">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5">
+        <v>2</v>
+      </c>
+      <c r="E2" s="5">
+        <v>3</v>
+      </c>
+      <c r="F2" s="5">
+        <v>4</v>
+      </c>
+      <c r="G2" s="5">
+        <v>5</v>
+      </c>
+      <c r="H2" s="5">
+        <v>6</v>
+      </c>
+      <c r="I2" s="5">
         <v>7</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="5">
         <v>8</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="6">
         <v>9</v>
       </c>
-      <c r="L2" s="10"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="13"/>
+      <c r="L2" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="7"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="9"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="14"/>
-      <c r="B3" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="15">
-        <v>4</v>
-      </c>
-      <c r="D3" s="15">
-        <v>5</v>
-      </c>
-      <c r="E3" s="15">
-        <v>4</v>
-      </c>
-      <c r="F3" s="15">
-        <v>3</v>
-      </c>
-      <c r="G3" s="15">
-        <v>4</v>
-      </c>
-      <c r="H3" s="15">
-        <v>4</v>
-      </c>
-      <c r="I3" s="15">
-        <v>3</v>
-      </c>
-      <c r="J3" s="15">
-        <v>4</v>
-      </c>
-      <c r="K3" s="16">
-        <v>5</v>
-      </c>
-      <c r="L3" s="17"/>
-      <c r="M3" s="18"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19"/>
+      <c r="A3" s="46"/>
+      <c r="B3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="10">
+        <v>4</v>
+      </c>
+      <c r="D3" s="10">
+        <v>5</v>
+      </c>
+      <c r="E3" s="10">
+        <v>4</v>
+      </c>
+      <c r="F3" s="10">
+        <v>3</v>
+      </c>
+      <c r="G3" s="10">
+        <v>4</v>
+      </c>
+      <c r="H3" s="10">
+        <v>4</v>
+      </c>
+      <c r="I3" s="10">
+        <v>3</v>
+      </c>
+      <c r="J3" s="10">
+        <v>4</v>
+      </c>
+      <c r="K3" s="11">
+        <v>5</v>
+      </c>
+      <c r="L3" s="41"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
     </row>
     <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="20"/>
-      <c r="B4" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="21">
-        <v>4</v>
-      </c>
-      <c r="D4" s="21">
-        <v>1</v>
-      </c>
-      <c r="E4" s="21">
-        <v>3</v>
-      </c>
-      <c r="F4" s="21">
+      <c r="A4" s="47"/>
+      <c r="B4" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="14">
+        <v>4</v>
+      </c>
+      <c r="D4" s="14">
+        <v>1</v>
+      </c>
+      <c r="E4" s="14">
+        <v>3</v>
+      </c>
+      <c r="F4" s="14">
         <v>9</v>
       </c>
-      <c r="G4" s="21">
-        <v>5</v>
-      </c>
-      <c r="H4" s="21">
+      <c r="G4" s="14">
+        <v>5</v>
+      </c>
+      <c r="H4" s="14">
         <v>7</v>
       </c>
-      <c r="I4" s="21">
+      <c r="I4" s="14">
         <v>8</v>
       </c>
-      <c r="J4" s="21">
-        <v>6</v>
-      </c>
-      <c r="K4" s="22">
-        <v>2</v>
-      </c>
-      <c r="L4" s="23"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
+      <c r="J4" s="14">
+        <v>6</v>
+      </c>
+      <c r="K4" s="15">
+        <v>2</v>
+      </c>
+      <c r="L4" s="42"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16">
+        <v>5</v>
+      </c>
+      <c r="D5" s="16">
+        <v>6</v>
+      </c>
+      <c r="E5" s="16">
+        <v>5</v>
+      </c>
+      <c r="F5" s="16">
+        <v>3</v>
+      </c>
+      <c r="G5" s="16">
+        <v>6</v>
+      </c>
+      <c r="H5" s="16">
         <v>7</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25">
-        <v>5</v>
-      </c>
-      <c r="D5" s="25">
-        <v>6</v>
-      </c>
-      <c r="E5" s="25">
-        <v>5</v>
-      </c>
-      <c r="F5" s="25">
-        <v>3</v>
-      </c>
-      <c r="G5" s="25">
-        <v>6</v>
-      </c>
-      <c r="H5" s="25">
+      <c r="I5" s="16">
+        <v>6</v>
+      </c>
+      <c r="J5" s="16">
         <v>7</v>
       </c>
-      <c r="I5" s="25">
-        <v>6</v>
-      </c>
-      <c r="J5" s="25">
-        <v>7</v>
-      </c>
-      <c r="K5" s="26">
-        <v>4</v>
-      </c>
-      <c r="L5" s="27"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
+      <c r="K5" s="17">
+        <v>4</v>
+      </c>
+      <c r="L5" s="43"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="30"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31">
-        <v>2</v>
-      </c>
-      <c r="D6" s="31">
-        <v>2</v>
-      </c>
-      <c r="E6" s="31">
-        <v>2</v>
-      </c>
-      <c r="F6" s="31">
-        <v>1</v>
-      </c>
-      <c r="G6" s="31">
-        <v>1</v>
-      </c>
-      <c r="H6" s="31">
-        <v>1</v>
-      </c>
-      <c r="I6" s="31">
-        <v>1</v>
-      </c>
-      <c r="J6" s="31">
-        <v>1</v>
-      </c>
-      <c r="K6" s="32">
-        <v>2</v>
-      </c>
-      <c r="L6" s="27">
+      <c r="A6" s="49"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21">
+        <v>2</v>
+      </c>
+      <c r="D6" s="21">
+        <v>2</v>
+      </c>
+      <c r="E6" s="21">
+        <v>2</v>
+      </c>
+      <c r="F6" s="21">
+        <v>1</v>
+      </c>
+      <c r="G6" s="21">
+        <v>1</v>
+      </c>
+      <c r="H6" s="21">
+        <v>1</v>
+      </c>
+      <c r="I6" s="21">
+        <v>1</v>
+      </c>
+      <c r="J6" s="21">
+        <v>1</v>
+      </c>
+      <c r="K6" s="22">
+        <v>2</v>
+      </c>
+      <c r="L6" s="18">
         <f>SUM(C6:K6)</f>
         <v>13</v>
       </c>
-      <c r="M6" s="28"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
     </row>
     <row r="7" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="33"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="35">
+      <c r="A7" s="50"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="24">
         <f>C5-C6</f>
         <v>3</v>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="24">
         <f t="shared" ref="D7:K7" si="0">D5-D6</f>
         <v>4</v>
       </c>
-      <c r="E7" s="35">
+      <c r="E7" s="24">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="24">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G7" s="34">
+      <c r="G7" s="23">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="H7" s="34">
+      <c r="H7" s="23">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I7" s="34">
+      <c r="I7" s="23">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="J7" s="34">
+      <c r="J7" s="23">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="K7" s="36">
+      <c r="K7" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="L7" s="27"/>
-      <c r="M7" s="28">
+      <c r="M7" s="19">
         <v>2.5</v>
       </c>
-      <c r="N7" s="29">
+      <c r="N7" s="20">
         <v>11.1</v>
       </c>
-      <c r="O7" s="19">
+      <c r="O7" s="13">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25">
-        <v>6</v>
-      </c>
-      <c r="D8" s="25">
-        <v>6</v>
-      </c>
-      <c r="E8" s="25">
-        <v>5</v>
-      </c>
-      <c r="F8" s="25">
-        <v>5</v>
-      </c>
-      <c r="G8" s="25">
-        <v>5</v>
-      </c>
-      <c r="H8" s="25">
-        <v>4</v>
-      </c>
-      <c r="I8" s="25">
-        <v>3</v>
-      </c>
-      <c r="J8" s="25">
-        <v>6</v>
-      </c>
-      <c r="K8" s="26">
+      <c r="A8" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16">
+        <v>6</v>
+      </c>
+      <c r="D8" s="16">
+        <v>6</v>
+      </c>
+      <c r="E8" s="16">
+        <v>5</v>
+      </c>
+      <c r="F8" s="16">
+        <v>5</v>
+      </c>
+      <c r="G8" s="16">
+        <v>5</v>
+      </c>
+      <c r="H8" s="16">
+        <v>4</v>
+      </c>
+      <c r="I8" s="16">
+        <v>3</v>
+      </c>
+      <c r="J8" s="16">
+        <v>6</v>
+      </c>
+      <c r="K8" s="17">
         <v>7</v>
       </c>
-      <c r="L8" s="27"/>
-      <c r="M8" s="28"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="19"/>
+      <c r="L8" s="43"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="13"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31">
-        <v>2</v>
-      </c>
-      <c r="D9" s="31">
-        <v>2</v>
-      </c>
-      <c r="E9" s="31">
-        <v>2</v>
-      </c>
-      <c r="F9" s="31">
-        <v>1</v>
-      </c>
-      <c r="G9" s="31">
-        <v>1</v>
-      </c>
-      <c r="H9" s="31">
-        <v>1</v>
-      </c>
-      <c r="I9" s="31">
-        <v>1</v>
-      </c>
-      <c r="J9" s="31">
-        <v>1</v>
-      </c>
-      <c r="K9" s="32">
-        <v>2</v>
-      </c>
-      <c r="L9" s="27">
+      <c r="A9" s="49"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21">
+        <v>2</v>
+      </c>
+      <c r="D9" s="21">
+        <v>2</v>
+      </c>
+      <c r="E9" s="21">
+        <v>2</v>
+      </c>
+      <c r="F9" s="21">
+        <v>1</v>
+      </c>
+      <c r="G9" s="21">
+        <v>1</v>
+      </c>
+      <c r="H9" s="21">
+        <v>1</v>
+      </c>
+      <c r="I9" s="21">
+        <v>1</v>
+      </c>
+      <c r="J9" s="21">
+        <v>1</v>
+      </c>
+      <c r="K9" s="22">
+        <v>2</v>
+      </c>
+      <c r="L9" s="18">
         <f>SUM(C9:K9)</f>
         <v>13</v>
       </c>
-      <c r="M9" s="28"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="13"/>
     </row>
     <row r="10" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="33"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34">
+      <c r="A10" s="50"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23">
         <f>C8-C9</f>
         <v>4</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="23">
         <f t="shared" ref="D10:K10" si="1">D8-D9</f>
         <v>4</v>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="24">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="23">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="23">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="H10" s="35">
+      <c r="H10" s="24">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="I10" s="35">
+      <c r="I10" s="24">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J10" s="34">
+      <c r="J10" s="23">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="K10" s="37">
+      <c r="K10" s="26">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="L10" s="27"/>
-      <c r="M10" s="28">
+      <c r="M10" s="19">
         <v>2.5</v>
       </c>
-      <c r="N10" s="29">
+      <c r="N10" s="20">
         <v>11.1</v>
       </c>
-      <c r="O10" s="19">
+      <c r="O10" s="13">
         <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25">
-        <v>4</v>
-      </c>
-      <c r="D11" s="25">
+      <c r="A11" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16">
+        <v>4</v>
+      </c>
+      <c r="D11" s="16">
         <v>7</v>
       </c>
-      <c r="E11" s="25">
-        <v>5</v>
-      </c>
-      <c r="F11" s="25">
-        <v>4</v>
-      </c>
-      <c r="G11" s="25">
-        <v>5</v>
-      </c>
-      <c r="H11" s="25">
-        <v>4</v>
-      </c>
-      <c r="I11" s="25">
-        <v>4</v>
-      </c>
-      <c r="J11" s="25">
-        <v>4</v>
-      </c>
-      <c r="K11" s="26">
-        <v>6</v>
-      </c>
-      <c r="L11" s="27"/>
-      <c r="M11" s="28"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="19"/>
+      <c r="E11" s="16">
+        <v>5</v>
+      </c>
+      <c r="F11" s="16">
+        <v>4</v>
+      </c>
+      <c r="G11" s="16">
+        <v>5</v>
+      </c>
+      <c r="H11" s="16">
+        <v>4</v>
+      </c>
+      <c r="I11" s="16">
+        <v>4</v>
+      </c>
+      <c r="J11" s="16">
+        <v>4</v>
+      </c>
+      <c r="K11" s="17">
+        <v>6</v>
+      </c>
+      <c r="L11" s="43"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="13"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="30"/>
-      <c r="B12" s="31"/>
-      <c r="C12" s="31">
-        <v>1</v>
-      </c>
-      <c r="D12" s="31">
-        <v>1</v>
-      </c>
-      <c r="E12" s="31">
-        <v>1</v>
-      </c>
-      <c r="F12" s="31">
+      <c r="A12" s="49"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21">
+        <v>1</v>
+      </c>
+      <c r="D12" s="21">
+        <v>1</v>
+      </c>
+      <c r="E12" s="21">
+        <v>1</v>
+      </c>
+      <c r="F12" s="21">
         <v>0</v>
       </c>
-      <c r="G12" s="31">
-        <v>1</v>
-      </c>
-      <c r="H12" s="31">
-        <v>1</v>
-      </c>
-      <c r="I12" s="31">
-        <v>1</v>
-      </c>
-      <c r="J12" s="31">
-        <v>1</v>
-      </c>
-      <c r="K12" s="32">
-        <v>1</v>
-      </c>
-      <c r="L12" s="27">
+      <c r="G12" s="21">
+        <v>1</v>
+      </c>
+      <c r="H12" s="21">
+        <v>1</v>
+      </c>
+      <c r="I12" s="21">
+        <v>1</v>
+      </c>
+      <c r="J12" s="21">
+        <v>1</v>
+      </c>
+      <c r="K12" s="22">
+        <v>1</v>
+      </c>
+      <c r="L12" s="18">
         <f>SUM(C12:K12)</f>
         <v>8</v>
       </c>
-      <c r="M12" s="28"/>
-      <c r="N12" s="29"/>
-      <c r="O12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="13"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="33"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="35">
+      <c r="A13" s="50"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="24">
         <f>C11-C12</f>
         <v>3</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="23">
         <f t="shared" ref="D13:K13" si="2">D11-D12</f>
         <v>6</v>
       </c>
-      <c r="E13" s="34">
+      <c r="E13" s="23">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="23">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="23">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="H13" s="35">
+      <c r="H13" s="24">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="I13" s="34">
+      <c r="I13" s="23">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="J13" s="35">
+      <c r="J13" s="24">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K13" s="37">
+      <c r="K13" s="26">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="L13" s="27"/>
-      <c r="M13" s="28">
-        <v>1</v>
-      </c>
-      <c r="N13" s="29">
+      <c r="M13" s="19">
+        <v>1</v>
+      </c>
+      <c r="N13" s="20">
         <v>4.4400000000000004</v>
       </c>
-      <c r="O13" s="19">
+      <c r="O13" s="13">
         <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25">
-        <v>5</v>
-      </c>
-      <c r="D14" s="25">
-        <v>6</v>
-      </c>
-      <c r="E14" s="25">
-        <v>6</v>
-      </c>
-      <c r="F14" s="25">
-        <v>3</v>
-      </c>
-      <c r="G14" s="25">
-        <v>5</v>
-      </c>
-      <c r="H14" s="25">
-        <v>5</v>
-      </c>
-      <c r="I14" s="25">
-        <v>5</v>
-      </c>
-      <c r="J14" s="25">
-        <v>5</v>
-      </c>
-      <c r="K14" s="26">
-        <v>6</v>
-      </c>
-      <c r="L14" s="27"/>
-      <c r="M14" s="28"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="19"/>
+      <c r="A14" s="48" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16">
+        <v>5</v>
+      </c>
+      <c r="D14" s="16">
+        <v>6</v>
+      </c>
+      <c r="E14" s="16">
+        <v>6</v>
+      </c>
+      <c r="F14" s="16">
+        <v>3</v>
+      </c>
+      <c r="G14" s="16">
+        <v>5</v>
+      </c>
+      <c r="H14" s="16">
+        <v>5</v>
+      </c>
+      <c r="I14" s="16">
+        <v>5</v>
+      </c>
+      <c r="J14" s="16">
+        <v>5</v>
+      </c>
+      <c r="K14" s="17">
+        <v>6</v>
+      </c>
+      <c r="L14" s="43"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="13"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="30"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31">
-        <v>2</v>
-      </c>
-      <c r="D15" s="31">
-        <v>2</v>
-      </c>
-      <c r="E15" s="31">
-        <v>2</v>
-      </c>
-      <c r="F15" s="31">
-        <v>1</v>
-      </c>
-      <c r="G15" s="31">
-        <v>2</v>
-      </c>
-      <c r="H15" s="31">
-        <v>1</v>
-      </c>
-      <c r="I15" s="31">
-        <v>1</v>
-      </c>
-      <c r="J15" s="31">
-        <v>2</v>
-      </c>
-      <c r="K15" s="32">
-        <v>2</v>
-      </c>
-      <c r="L15" s="27">
+      <c r="A15" s="49"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21">
+        <v>2</v>
+      </c>
+      <c r="D15" s="21">
+        <v>2</v>
+      </c>
+      <c r="E15" s="21">
+        <v>2</v>
+      </c>
+      <c r="F15" s="21">
+        <v>1</v>
+      </c>
+      <c r="G15" s="21">
+        <v>2</v>
+      </c>
+      <c r="H15" s="21">
+        <v>1</v>
+      </c>
+      <c r="I15" s="21">
+        <v>1</v>
+      </c>
+      <c r="J15" s="21">
+        <v>2</v>
+      </c>
+      <c r="K15" s="22">
+        <v>2</v>
+      </c>
+      <c r="L15" s="18">
         <f>SUM(C15:K15)</f>
         <v>15</v>
       </c>
-      <c r="M15" s="28"/>
-      <c r="N15" s="29"/>
-      <c r="O15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="13"/>
     </row>
     <row r="16" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="33"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="35">
+      <c r="A16" s="50"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="24">
         <f>C14-C15</f>
         <v>3</v>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="24">
         <f t="shared" ref="D16:K16" si="3">D14-D15</f>
         <v>4</v>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="23">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="24">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="G16" s="34">
+      <c r="G16" s="23">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="H16" s="34">
+      <c r="H16" s="23">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="I16" s="34">
+      <c r="I16" s="23">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="J16" s="35">
+      <c r="J16" s="24">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="K16" s="37">
+      <c r="K16" s="26">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="L16" s="27"/>
-      <c r="M16" s="28">
+      <c r="M16" s="19">
         <v>0.5</v>
       </c>
-      <c r="N16" s="29">
+      <c r="N16" s="20">
         <v>2.2200000000000002</v>
       </c>
-      <c r="O16" s="19">
+      <c r="O16" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25">
-        <v>6</v>
-      </c>
-      <c r="D17" s="25">
-        <v>6</v>
-      </c>
-      <c r="E17" s="25">
-        <v>5</v>
-      </c>
-      <c r="F17" s="25">
-        <v>4</v>
-      </c>
-      <c r="G17" s="25">
-        <v>6</v>
-      </c>
-      <c r="H17" s="25">
-        <v>5</v>
-      </c>
-      <c r="I17" s="25">
-        <v>3</v>
-      </c>
-      <c r="J17" s="25">
-        <v>5</v>
-      </c>
-      <c r="K17" s="26">
-        <v>6</v>
-      </c>
-      <c r="L17" s="27"/>
-      <c r="M17" s="28"/>
-      <c r="N17" s="29"/>
-      <c r="O17" s="19"/>
+      <c r="A17" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16">
+        <v>6</v>
+      </c>
+      <c r="D17" s="16">
+        <v>6</v>
+      </c>
+      <c r="E17" s="16">
+        <v>5</v>
+      </c>
+      <c r="F17" s="16">
+        <v>4</v>
+      </c>
+      <c r="G17" s="16">
+        <v>6</v>
+      </c>
+      <c r="H17" s="16">
+        <v>5</v>
+      </c>
+      <c r="I17" s="16">
+        <v>3</v>
+      </c>
+      <c r="J17" s="16">
+        <v>5</v>
+      </c>
+      <c r="K17" s="17">
+        <v>6</v>
+      </c>
+      <c r="L17" s="43"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="13"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="30"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31">
-        <v>1</v>
-      </c>
-      <c r="D18" s="31">
-        <v>2</v>
-      </c>
-      <c r="E18" s="31">
-        <v>1</v>
-      </c>
-      <c r="F18" s="31">
-        <v>1</v>
-      </c>
-      <c r="G18" s="31">
-        <v>1</v>
-      </c>
-      <c r="H18" s="31">
-        <v>1</v>
-      </c>
-      <c r="I18" s="31">
-        <v>1</v>
-      </c>
-      <c r="J18" s="31">
-        <v>1</v>
-      </c>
-      <c r="K18" s="32">
-        <v>1</v>
-      </c>
-      <c r="L18" s="27">
+      <c r="A18" s="49"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21">
+        <v>1</v>
+      </c>
+      <c r="D18" s="21">
+        <v>2</v>
+      </c>
+      <c r="E18" s="21">
+        <v>1</v>
+      </c>
+      <c r="F18" s="21">
+        <v>1</v>
+      </c>
+      <c r="G18" s="21">
+        <v>1</v>
+      </c>
+      <c r="H18" s="21">
+        <v>1</v>
+      </c>
+      <c r="I18" s="21">
+        <v>1</v>
+      </c>
+      <c r="J18" s="21">
+        <v>1</v>
+      </c>
+      <c r="K18" s="22">
+        <v>1</v>
+      </c>
+      <c r="L18" s="18">
         <f>SUM(C18:K18)</f>
         <v>10</v>
       </c>
-      <c r="M18" s="28"/>
-      <c r="N18" s="29"/>
-      <c r="O18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="13"/>
     </row>
     <row r="19" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="33"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34">
+      <c r="A19" s="50"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23">
         <f>C17-C18</f>
         <v>5</v>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="24">
         <f t="shared" ref="D19:K19" si="4">D17-D18</f>
         <v>4</v>
       </c>
-      <c r="E19" s="34">
+      <c r="E19" s="23">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="F19" s="34">
+      <c r="F19" s="23">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="23">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="H19" s="34">
+      <c r="H19" s="23">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="I19" s="35">
+      <c r="I19" s="24">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="J19" s="34">
+      <c r="J19" s="23">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="K19" s="37">
+      <c r="K19" s="26">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="L19" s="27"/>
-      <c r="M19" s="28">
+      <c r="M19" s="19">
         <v>0.5</v>
       </c>
-      <c r="N19" s="29">
+      <c r="N19" s="20">
         <v>2.2200000000000002</v>
       </c>
-      <c r="O19" s="19">
+      <c r="O19" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25">
-        <v>5</v>
-      </c>
-      <c r="D20" s="25">
-        <v>6</v>
-      </c>
-      <c r="E20" s="25">
-        <v>6</v>
-      </c>
-      <c r="F20" s="25">
-        <v>3</v>
-      </c>
-      <c r="G20" s="25">
+      <c r="A20" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16">
+        <v>5</v>
+      </c>
+      <c r="D20" s="16">
+        <v>6</v>
+      </c>
+      <c r="E20" s="16">
+        <v>6</v>
+      </c>
+      <c r="F20" s="16">
+        <v>3</v>
+      </c>
+      <c r="G20" s="16">
         <v>7</v>
       </c>
-      <c r="H20" s="25">
-        <v>5</v>
-      </c>
-      <c r="I20" s="25">
-        <v>4</v>
-      </c>
-      <c r="J20" s="25">
-        <v>5</v>
-      </c>
-      <c r="K20" s="26">
-        <v>6</v>
-      </c>
-      <c r="L20" s="27"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="19"/>
+      <c r="H20" s="16">
+        <v>5</v>
+      </c>
+      <c r="I20" s="16">
+        <v>4</v>
+      </c>
+      <c r="J20" s="16">
+        <v>5</v>
+      </c>
+      <c r="K20" s="17">
+        <v>6</v>
+      </c>
+      <c r="L20" s="43"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="13"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="30"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31">
-        <v>1</v>
-      </c>
-      <c r="D21" s="31">
-        <v>1</v>
-      </c>
-      <c r="E21" s="31">
-        <v>1</v>
-      </c>
-      <c r="F21" s="31">
+      <c r="A21" s="49"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21">
+        <v>1</v>
+      </c>
+      <c r="D21" s="21">
+        <v>1</v>
+      </c>
+      <c r="E21" s="21">
+        <v>1</v>
+      </c>
+      <c r="F21" s="21">
         <v>0</v>
       </c>
-      <c r="G21" s="31">
-        <v>1</v>
-      </c>
-      <c r="H21" s="31">
-        <v>1</v>
-      </c>
-      <c r="I21" s="31">
-        <v>1</v>
-      </c>
-      <c r="J21" s="31">
-        <v>1</v>
-      </c>
-      <c r="K21" s="32">
-        <v>1</v>
-      </c>
-      <c r="L21" s="27">
+      <c r="G21" s="21">
+        <v>1</v>
+      </c>
+      <c r="H21" s="21">
+        <v>1</v>
+      </c>
+      <c r="I21" s="21">
+        <v>1</v>
+      </c>
+      <c r="J21" s="21">
+        <v>1</v>
+      </c>
+      <c r="K21" s="22">
+        <v>1</v>
+      </c>
+      <c r="L21" s="18">
         <f>SUM(C21:K21)</f>
         <v>8</v>
       </c>
-      <c r="M21" s="28"/>
-      <c r="N21" s="29"/>
-      <c r="O21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="13"/>
     </row>
     <row r="22" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="33"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="34">
+      <c r="A22" s="50"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23">
         <f>C20-C21</f>
         <v>4</v>
       </c>
-      <c r="D22" s="34">
+      <c r="D22" s="23">
         <f t="shared" ref="D22:K22" si="5">D20-D21</f>
         <v>5</v>
       </c>
-      <c r="E22" s="34">
+      <c r="E22" s="23">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="F22" s="34">
+      <c r="F22" s="23">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="G22" s="34">
+      <c r="G22" s="23">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="H22" s="34">
+      <c r="H22" s="23">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="I22" s="34">
+      <c r="I22" s="23">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="J22" s="34">
+      <c r="J22" s="23">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="K22" s="37">
+      <c r="K22" s="26">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="L22" s="27"/>
-      <c r="M22" s="28">
+      <c r="M22" s="19">
         <v>0</v>
       </c>
-      <c r="N22" s="29"/>
-      <c r="O22" s="19"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25">
-        <v>6</v>
-      </c>
-      <c r="D23" s="25">
+      <c r="A23" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16">
+        <v>6</v>
+      </c>
+      <c r="D23" s="16">
         <v>8</v>
       </c>
-      <c r="E23" s="25">
+      <c r="E23" s="16">
         <v>8</v>
       </c>
-      <c r="F23" s="25">
-        <v>4</v>
-      </c>
-      <c r="G23" s="25">
-        <v>4</v>
-      </c>
-      <c r="H23" s="25">
-        <v>6</v>
-      </c>
-      <c r="I23" s="25">
-        <v>5</v>
-      </c>
-      <c r="J23" s="25">
-        <v>6</v>
-      </c>
-      <c r="K23" s="26">
+      <c r="F23" s="16">
+        <v>4</v>
+      </c>
+      <c r="G23" s="16">
+        <v>4</v>
+      </c>
+      <c r="H23" s="16">
+        <v>6</v>
+      </c>
+      <c r="I23" s="16">
+        <v>5</v>
+      </c>
+      <c r="J23" s="16">
+        <v>6</v>
+      </c>
+      <c r="K23" s="17">
         <v>7</v>
       </c>
-      <c r="L23" s="27"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="19"/>
+      <c r="L23" s="43"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="13"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="30"/>
-      <c r="B24" s="31"/>
-      <c r="C24" s="31">
-        <v>3</v>
-      </c>
-      <c r="D24" s="31">
-        <v>3</v>
-      </c>
-      <c r="E24" s="31">
-        <v>3</v>
-      </c>
-      <c r="F24" s="31">
-        <v>2</v>
-      </c>
-      <c r="G24" s="31">
-        <v>2</v>
-      </c>
-      <c r="H24" s="31">
-        <v>2</v>
-      </c>
-      <c r="I24" s="31">
-        <v>2</v>
-      </c>
-      <c r="J24" s="31">
-        <v>2</v>
-      </c>
-      <c r="K24" s="32">
-        <v>3</v>
-      </c>
-      <c r="L24" s="27">
+      <c r="A24" s="49"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21">
+        <v>3</v>
+      </c>
+      <c r="D24" s="21">
+        <v>3</v>
+      </c>
+      <c r="E24" s="21">
+        <v>3</v>
+      </c>
+      <c r="F24" s="21">
+        <v>2</v>
+      </c>
+      <c r="G24" s="21">
+        <v>2</v>
+      </c>
+      <c r="H24" s="21">
+        <v>2</v>
+      </c>
+      <c r="I24" s="21">
+        <v>2</v>
+      </c>
+      <c r="J24" s="21">
+        <v>2</v>
+      </c>
+      <c r="K24" s="22">
+        <v>3</v>
+      </c>
+      <c r="L24" s="18">
         <f>SUM(C24:K24)</f>
         <v>22</v>
       </c>
-      <c r="M24" s="28"/>
-      <c r="N24" s="29"/>
-      <c r="O24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="13"/>
     </row>
     <row r="25" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="33"/>
-      <c r="B25" s="34"/>
-      <c r="C25" s="35">
+      <c r="A25" s="50"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="24">
         <f>C23-C24</f>
         <v>3</v>
       </c>
-      <c r="D25" s="34">
+      <c r="D25" s="23">
         <f t="shared" ref="D25:K25" si="6">D23-D24</f>
         <v>5</v>
       </c>
-      <c r="E25" s="34">
+      <c r="E25" s="23">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="F25" s="35">
+      <c r="F25" s="24">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="G25" s="35">
+      <c r="G25" s="24">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="H25" s="34">
+      <c r="H25" s="23">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="I25" s="34">
+      <c r="I25" s="23">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="J25" s="34">
+      <c r="J25" s="23">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="K25" s="37">
+      <c r="K25" s="26">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="L25" s="27"/>
-      <c r="M25" s="28">
-        <v>2</v>
-      </c>
-      <c r="N25" s="29">
+      <c r="M25" s="19">
+        <v>2</v>
+      </c>
+      <c r="N25" s="20">
         <v>8.8800000000000008</v>
       </c>
-      <c r="O25" s="19">
+      <c r="O25" s="13">
         <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25">
+      <c r="A26" s="48" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16">
         <v>8</v>
       </c>
-      <c r="D26" s="25">
+      <c r="D26" s="16">
         <v>7</v>
       </c>
-      <c r="E26" s="25">
-        <v>6</v>
-      </c>
-      <c r="F26" s="25">
-        <v>4</v>
-      </c>
-      <c r="G26" s="25">
-        <v>6</v>
-      </c>
-      <c r="H26" s="25">
+      <c r="E26" s="16">
+        <v>6</v>
+      </c>
+      <c r="F26" s="16">
+        <v>4</v>
+      </c>
+      <c r="G26" s="16">
+        <v>6</v>
+      </c>
+      <c r="H26" s="16">
         <v>8</v>
       </c>
-      <c r="I26" s="25">
-        <v>4</v>
-      </c>
-      <c r="J26" s="25">
-        <v>6</v>
-      </c>
-      <c r="K26" s="26">
-        <v>5</v>
-      </c>
-      <c r="L26" s="27"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="19"/>
+      <c r="I26" s="16">
+        <v>4</v>
+      </c>
+      <c r="J26" s="16">
+        <v>6</v>
+      </c>
+      <c r="K26" s="17">
+        <v>5</v>
+      </c>
+      <c r="L26" s="18"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="13"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="30"/>
-      <c r="B27" s="31"/>
-      <c r="C27" s="31">
-        <v>2</v>
-      </c>
-      <c r="D27" s="31">
-        <v>2</v>
-      </c>
-      <c r="E27" s="31">
-        <v>2</v>
-      </c>
-      <c r="F27" s="31">
-        <v>1</v>
-      </c>
-      <c r="G27" s="31">
-        <v>2</v>
-      </c>
-      <c r="H27" s="31">
-        <v>1</v>
-      </c>
-      <c r="I27" s="31">
-        <v>1</v>
-      </c>
-      <c r="J27" s="31">
-        <v>2</v>
-      </c>
-      <c r="K27" s="32">
-        <v>2</v>
-      </c>
-      <c r="L27" s="27">
+      <c r="A27" s="49"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21">
+        <v>2</v>
+      </c>
+      <c r="D27" s="21">
+        <v>2</v>
+      </c>
+      <c r="E27" s="21">
+        <v>2</v>
+      </c>
+      <c r="F27" s="21">
+        <v>1</v>
+      </c>
+      <c r="G27" s="21">
+        <v>2</v>
+      </c>
+      <c r="H27" s="21">
+        <v>1</v>
+      </c>
+      <c r="I27" s="21">
+        <v>1</v>
+      </c>
+      <c r="J27" s="21">
+        <v>2</v>
+      </c>
+      <c r="K27" s="22">
+        <v>2</v>
+      </c>
+      <c r="L27" s="18">
         <f>SUM(C27:K27)</f>
         <v>15</v>
       </c>
-      <c r="M27" s="28"/>
-      <c r="N27" s="29"/>
-      <c r="O27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="13"/>
     </row>
     <row r="28" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="33"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34">
+      <c r="A28" s="50"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23">
         <f>C26-C27</f>
         <v>6</v>
       </c>
-      <c r="D28" s="34">
+      <c r="D28" s="23">
         <f t="shared" ref="D28:K28" si="7">D26-D27</f>
         <v>5</v>
       </c>
-      <c r="E28" s="34">
+      <c r="E28" s="23">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="F28" s="34">
+      <c r="F28" s="23">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="G28" s="34">
+      <c r="G28" s="23">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="H28" s="34">
+      <c r="H28" s="23">
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="I28" s="34">
+      <c r="I28" s="23">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="J28" s="34">
+      <c r="J28" s="23">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="K28" s="34">
+      <c r="K28" s="23">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="L28" s="38"/>
-      <c r="M28" s="39">
+      <c r="L28" s="27"/>
+      <c r="M28" s="28">
         <v>0</v>
       </c>
-      <c r="N28" s="40"/>
-      <c r="O28" s="41"/>
+      <c r="N28" s="29"/>
+      <c r="O28" s="30">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="42"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="42"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="42"/>
-      <c r="K29" s="42"/>
-      <c r="L29" s="42"/>
-      <c r="M29" s="43"/>
-      <c r="N29" s="44"/>
-      <c r="O29" s="45"/>
+      <c r="A29" s="32"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="32"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="32"/>
+      <c r="O29" s="33"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="42"/>
-      <c r="B30" s="42"/>
-      <c r="C30" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="F30" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="G30" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="H30" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="I30" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="J30" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="K30" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="L30" s="42"/>
-      <c r="M30" s="43"/>
-      <c r="N30" s="46">
+      <c r="A30" s="32"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="G30" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="J30" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="K30" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="L30" s="39"/>
+      <c r="M30" s="36"/>
+      <c r="N30" s="37">
         <f>SUM(N7:N29)</f>
         <v>39.96</v>
       </c>
-      <c r="O30" s="47">
+      <c r="O30" s="38">
         <f>SUM(O7:O29)</f>
         <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="42"/>
-      <c r="B31" s="42"/>
-      <c r="C31" s="42"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="42" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="42"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="I31" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="J31" s="42" t="s">
+      <c r="A31" s="32"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="K31" s="42"/>
-      <c r="L31" s="42"/>
-      <c r="M31" s="43"/>
-      <c r="N31" s="44"/>
-      <c r="O31" s="44"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="I31" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="J31" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="K31" s="39"/>
+      <c r="L31" s="39"/>
+      <c r="M31" s="36"/>
+      <c r="N31" s="39"/>
+      <c r="O31" s="39"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="L2:L4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/results/2025/Week 7 Skins.xlsx
+++ b/public/results/2025/Week 7 Skins.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amentumcms-my.sharepoint.com/personal/mark_hutter_amentumcms_com/Documents/DATA/Code/golf-league-site/public/results/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{DBBB26E3-A62B-4C64-B177-E34D2F1A43A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EAD785F-3944-4B43-BE06-68E9C61988DB}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="8_{DBBB26E3-A62B-4C64-B177-E34D2F1A43A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24DF8014-0358-4F9B-A5F0-CBC41013F47E}"/>
   <bookViews>
-    <workbookView xWindow="43470" yWindow="3600" windowWidth="26730" windowHeight="18000" xr2:uid="{F705A57A-943D-4C93-A0B0-17476496A7BD}"/>
+    <workbookView xWindow="7515" yWindow="2640" windowWidth="26730" windowHeight="18000" xr2:uid="{F705A57A-943D-4C93-A0B0-17476496A7BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 7 Skins" sheetId="1" r:id="rId1"/>
@@ -83,9 +83,6 @@
     <t>Mark Y</t>
   </si>
   <si>
-    <t>Ton A</t>
-  </si>
-  <si>
     <t>Ryan M</t>
   </si>
   <si>
@@ -111,6 +108,9 @@
   </si>
   <si>
     <t>Tony (.5)</t>
+  </si>
+  <si>
+    <t>Tony A</t>
   </si>
 </sst>
 </file>
@@ -658,12 +658,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -676,6 +670,36 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
@@ -684,30 +708,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1051,28 +1051,28 @@
   <dimension ref="A1:O31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="44"/>
-    <col min="3" max="11" width="8.7109375" style="44" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" style="44" customWidth="1"/>
-    <col min="13" max="13" width="5.85546875" style="44" customWidth="1"/>
-    <col min="14" max="15" width="6.5703125" style="44" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="44"/>
+    <col min="1" max="2" width="9.140625" style="39"/>
+    <col min="3" max="11" width="8.7109375" style="39" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" style="39" customWidth="1"/>
+    <col min="13" max="13" width="5.85546875" style="39" customWidth="1"/>
+    <col min="14" max="15" width="6.5703125" style="39" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="39"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
       <c r="L1" s="1"/>
       <c r="M1" s="2" t="s">
         <v>1</v>
@@ -1083,7 +1083,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="40" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -1116,15 +1116,15 @@
       <c r="K2" s="6">
         <v>9</v>
       </c>
-      <c r="L2" s="40" t="s">
-        <v>22</v>
+      <c r="L2" s="48" t="s">
+        <v>21</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="8"/>
       <c r="O2" s="9"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="46"/>
+      <c r="A3" s="41"/>
       <c r="B3" s="10" t="s">
         <v>5</v>
       </c>
@@ -1155,13 +1155,13 @@
       <c r="K3" s="11">
         <v>5</v>
       </c>
-      <c r="L3" s="41"/>
+      <c r="L3" s="49"/>
       <c r="M3" s="12"/>
       <c r="N3" s="13"/>
       <c r="O3" s="13"/>
     </row>
     <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="47"/>
+      <c r="A4" s="42"/>
       <c r="B4" s="14" t="s">
         <v>6</v>
       </c>
@@ -1192,13 +1192,13 @@
       <c r="K4" s="15">
         <v>2</v>
       </c>
-      <c r="L4" s="42"/>
+      <c r="L4" s="50"/>
       <c r="M4" s="12"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="43" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="16"/>
@@ -1229,13 +1229,13 @@
       <c r="K5" s="17">
         <v>4</v>
       </c>
-      <c r="L5" s="43"/>
+      <c r="L5" s="38"/>
       <c r="M5" s="19"/>
       <c r="N5" s="20"/>
       <c r="O5" s="20"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="49"/>
+      <c r="A6" s="44"/>
       <c r="B6" s="21"/>
       <c r="C6" s="21">
         <v>2</v>
@@ -1273,7 +1273,7 @@
       <c r="O6" s="20"/>
     </row>
     <row r="7" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="50"/>
+      <c r="A7" s="45"/>
       <c r="B7" s="23"/>
       <c r="C7" s="24">
         <f>C5-C6</f>
@@ -1323,8 +1323,8 @@
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="48" t="s">
-        <v>15</v>
+      <c r="A8" s="43" t="s">
+        <v>24</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="16">
@@ -1354,13 +1354,13 @@
       <c r="K8" s="17">
         <v>7</v>
       </c>
-      <c r="L8" s="43"/>
+      <c r="L8" s="38"/>
       <c r="M8" s="19"/>
       <c r="N8" s="20"/>
       <c r="O8" s="13"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="49"/>
+      <c r="A9" s="44"/>
       <c r="B9" s="21"/>
       <c r="C9" s="21">
         <v>2</v>
@@ -1398,7 +1398,7 @@
       <c r="O9" s="13"/>
     </row>
     <row r="10" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="50"/>
+      <c r="A10" s="45"/>
       <c r="B10" s="23"/>
       <c r="C10" s="23">
         <f>C8-C9</f>
@@ -1448,8 +1448,8 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="48" t="s">
-        <v>16</v>
+      <c r="A11" s="43" t="s">
+        <v>15</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="16">
@@ -1479,13 +1479,13 @@
       <c r="K11" s="17">
         <v>6</v>
       </c>
-      <c r="L11" s="43"/>
+      <c r="L11" s="38"/>
       <c r="M11" s="19"/>
       <c r="N11" s="20"/>
       <c r="O11" s="13"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="49"/>
+      <c r="A12" s="44"/>
       <c r="B12" s="21"/>
       <c r="C12" s="21">
         <v>1</v>
@@ -1523,7 +1523,7 @@
       <c r="O12" s="13"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="50"/>
+      <c r="A13" s="45"/>
       <c r="B13" s="23"/>
       <c r="C13" s="24">
         <f>C11-C12</f>
@@ -1573,8 +1573,8 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="48" t="s">
-        <v>17</v>
+      <c r="A14" s="43" t="s">
+        <v>16</v>
       </c>
       <c r="B14" s="16"/>
       <c r="C14" s="16">
@@ -1604,13 +1604,13 @@
       <c r="K14" s="17">
         <v>6</v>
       </c>
-      <c r="L14" s="43"/>
+      <c r="L14" s="38"/>
       <c r="M14" s="19"/>
       <c r="N14" s="20"/>
       <c r="O14" s="13"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="49"/>
+      <c r="A15" s="44"/>
       <c r="B15" s="21"/>
       <c r="C15" s="21">
         <v>2</v>
@@ -1648,7 +1648,7 @@
       <c r="O15" s="13"/>
     </row>
     <row r="16" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="50"/>
+      <c r="A16" s="45"/>
       <c r="B16" s="23"/>
       <c r="C16" s="24">
         <f>C14-C15</f>
@@ -1698,8 +1698,8 @@
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="48" t="s">
-        <v>18</v>
+      <c r="A17" s="43" t="s">
+        <v>17</v>
       </c>
       <c r="B17" s="16"/>
       <c r="C17" s="16">
@@ -1729,13 +1729,13 @@
       <c r="K17" s="17">
         <v>6</v>
       </c>
-      <c r="L17" s="43"/>
+      <c r="L17" s="38"/>
       <c r="M17" s="19"/>
       <c r="N17" s="20"/>
       <c r="O17" s="13"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="49"/>
+      <c r="A18" s="44"/>
       <c r="B18" s="21"/>
       <c r="C18" s="21">
         <v>1</v>
@@ -1773,7 +1773,7 @@
       <c r="O18" s="13"/>
     </row>
     <row r="19" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="50"/>
+      <c r="A19" s="45"/>
       <c r="B19" s="23"/>
       <c r="C19" s="23">
         <f>C17-C18</f>
@@ -1823,8 +1823,8 @@
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="48" t="s">
-        <v>19</v>
+      <c r="A20" s="43" t="s">
+        <v>18</v>
       </c>
       <c r="B20" s="16"/>
       <c r="C20" s="16">
@@ -1854,13 +1854,13 @@
       <c r="K20" s="17">
         <v>6</v>
       </c>
-      <c r="L20" s="43"/>
+      <c r="L20" s="38"/>
       <c r="M20" s="19"/>
       <c r="N20" s="20"/>
       <c r="O20" s="13"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="49"/>
+      <c r="A21" s="44"/>
       <c r="B21" s="21"/>
       <c r="C21" s="21">
         <v>1</v>
@@ -1898,7 +1898,7 @@
       <c r="O21" s="13"/>
     </row>
     <row r="22" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="50"/>
+      <c r="A22" s="45"/>
       <c r="B22" s="23"/>
       <c r="C22" s="23">
         <f>C20-C21</f>
@@ -1946,8 +1946,8 @@
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="48" t="s">
-        <v>20</v>
+      <c r="A23" s="43" t="s">
+        <v>19</v>
       </c>
       <c r="B23" s="16"/>
       <c r="C23" s="16">
@@ -1977,13 +1977,13 @@
       <c r="K23" s="17">
         <v>7</v>
       </c>
-      <c r="L23" s="43"/>
+      <c r="L23" s="38"/>
       <c r="M23" s="19"/>
       <c r="N23" s="20"/>
       <c r="O23" s="13"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="49"/>
+      <c r="A24" s="44"/>
       <c r="B24" s="21"/>
       <c r="C24" s="21">
         <v>3</v>
@@ -2021,7 +2021,7 @@
       <c r="O24" s="13"/>
     </row>
     <row r="25" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="50"/>
+      <c r="A25" s="45"/>
       <c r="B25" s="23"/>
       <c r="C25" s="24">
         <f>C23-C24</f>
@@ -2071,8 +2071,8 @@
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="48" t="s">
-        <v>21</v>
+      <c r="A26" s="43" t="s">
+        <v>20</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="16">
@@ -2108,7 +2108,7 @@
       <c r="O26" s="13"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="49"/>
+      <c r="A27" s="44"/>
       <c r="B27" s="21"/>
       <c r="C27" s="21">
         <v>2</v>
@@ -2146,7 +2146,7 @@
       <c r="O27" s="13"/>
     </row>
     <row r="28" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="50"/>
+      <c r="A28" s="45"/>
       <c r="B28" s="23"/>
       <c r="C28" s="23">
         <f>C26-C27</f>
@@ -2213,40 +2213,40 @@
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="32"/>
       <c r="B30" s="32"/>
-      <c r="C30" s="39" t="s">
+      <c r="C30" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="D30" s="39" t="s">
+      <c r="D30" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="39" t="s">
+      <c r="E30" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F30" s="39" t="s">
+      <c r="F30" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="G30" s="39" t="s">
+      <c r="G30" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="H30" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="I30" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="J30" s="39" t="s">
+      <c r="H30" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="I30" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="K30" s="39" t="s">
+      <c r="K30" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="L30" s="39"/>
-      <c r="M30" s="36"/>
-      <c r="N30" s="37">
+      <c r="L30" s="37"/>
+      <c r="M30" s="34"/>
+      <c r="N30" s="35">
         <f>SUM(N7:N29)</f>
         <v>39.96</v>
       </c>
-      <c r="O30" s="38">
+      <c r="O30" s="36">
         <f>SUM(O7:O29)</f>
         <v>39</v>
       </c>
@@ -2254,27 +2254,27 @@
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="32"/>
       <c r="B31" s="32"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F31" s="39"/>
-      <c r="G31" s="39"/>
-      <c r="H31" s="39" t="s">
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="37"/>
+      <c r="G31" s="37"/>
+      <c r="H31" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="I31" s="39" t="s">
+      <c r="I31" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="J31" s="39" t="s">
+      <c r="J31" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="K31" s="39"/>
-      <c r="L31" s="39"/>
-      <c r="M31" s="36"/>
-      <c r="N31" s="39"/>
-      <c r="O31" s="39"/>
+      <c r="K31" s="37"/>
+      <c r="L31" s="37"/>
+      <c r="M31" s="34"/>
+      <c r="N31" s="37"/>
+      <c r="O31" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/public/results/2025/Week 7 Skins.xlsx
+++ b/public/results/2025/Week 7 Skins.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amentumcms-my.sharepoint.com/personal/mark_hutter_amentumcms_com/Documents/DATA/Code/golf-league-site/public/results/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="8_{DBBB26E3-A62B-4C64-B177-E34D2F1A43A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24DF8014-0358-4F9B-A5F0-CBC41013F47E}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="8_{DBBB26E3-A62B-4C64-B177-E34D2F1A43A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00FCE3B6-7C91-4C88-B84D-7D8AA5376D69}"/>
   <bookViews>
-    <workbookView xWindow="7515" yWindow="2640" windowWidth="26730" windowHeight="18000" xr2:uid="{F705A57A-943D-4C93-A0B0-17476496A7BD}"/>
+    <workbookView xWindow="7170" yWindow="2295" windowWidth="26730" windowHeight="18000" xr2:uid="{F705A57A-943D-4C93-A0B0-17476496A7BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 7 Skins" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="28">
   <si>
     <t>Skins ($40) $4.44/hole</t>
   </si>
@@ -111,6 +111,15 @@
   </si>
   <si>
     <t>Tony A</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Strokes</t>
+  </si>
+  <si>
+    <t>Net</t>
   </si>
 </sst>
 </file>
@@ -120,7 +129,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,6 +189,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -557,7 +572,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -708,6 +723,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1052,7 +1076,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="39"/>
-    <col min="3" max="11" width="8.7109375" style="39" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" style="39" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" style="39" customWidth="1"/>
+    <col min="5" max="5" width="10" style="39" customWidth="1"/>
+    <col min="6" max="6" width="7.42578125" style="39" customWidth="1"/>
+    <col min="7" max="11" width="8.7109375" style="39" customWidth="1"/>
     <col min="12" max="12" width="4.28515625" style="39" customWidth="1"/>
     <col min="13" max="13" width="5.85546875" style="39" customWidth="1"/>
     <col min="14" max="15" width="6.5703125" style="39" customWidth="1"/>
@@ -1201,7 +1229,9 @@
       <c r="A5" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="16"/>
+      <c r="B5" s="51" t="s">
+        <v>25</v>
+      </c>
       <c r="C5" s="16">
         <v>5</v>
       </c>
@@ -1236,7 +1266,9 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="44"/>
-      <c r="B6" s="21"/>
+      <c r="B6" s="52" t="s">
+        <v>26</v>
+      </c>
       <c r="C6" s="21">
         <v>2</v>
       </c>
@@ -1274,7 +1306,9 @@
     </row>
     <row r="7" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="45"/>
-      <c r="B7" s="23"/>
+      <c r="B7" s="53" t="s">
+        <v>27</v>
+      </c>
       <c r="C7" s="24">
         <f>C5-C6</f>
         <v>3</v>
@@ -1326,7 +1360,9 @@
       <c r="A8" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="16"/>
+      <c r="B8" s="51" t="s">
+        <v>25</v>
+      </c>
       <c r="C8" s="16">
         <v>6</v>
       </c>
@@ -1361,7 +1397,9 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="44"/>
-      <c r="B9" s="21"/>
+      <c r="B9" s="52" t="s">
+        <v>26</v>
+      </c>
       <c r="C9" s="21">
         <v>2</v>
       </c>
@@ -1399,7 +1437,9 @@
     </row>
     <row r="10" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="45"/>
-      <c r="B10" s="23"/>
+      <c r="B10" s="53" t="s">
+        <v>27</v>
+      </c>
       <c r="C10" s="23">
         <f>C8-C9</f>
         <v>4</v>
@@ -1451,7 +1491,9 @@
       <c r="A11" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="16"/>
+      <c r="B11" s="51" t="s">
+        <v>25</v>
+      </c>
       <c r="C11" s="16">
         <v>4</v>
       </c>
@@ -1486,7 +1528,9 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="44"/>
-      <c r="B12" s="21"/>
+      <c r="B12" s="52" t="s">
+        <v>26</v>
+      </c>
       <c r="C12" s="21">
         <v>1</v>
       </c>
@@ -1524,7 +1568,9 @@
     </row>
     <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="45"/>
-      <c r="B13" s="23"/>
+      <c r="B13" s="53" t="s">
+        <v>27</v>
+      </c>
       <c r="C13" s="24">
         <f>C11-C12</f>
         <v>3</v>
@@ -1576,7 +1622,9 @@
       <c r="A14" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="16"/>
+      <c r="B14" s="51" t="s">
+        <v>25</v>
+      </c>
       <c r="C14" s="16">
         <v>5</v>
       </c>
@@ -1611,7 +1659,9 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="44"/>
-      <c r="B15" s="21"/>
+      <c r="B15" s="52" t="s">
+        <v>26</v>
+      </c>
       <c r="C15" s="21">
         <v>2</v>
       </c>
@@ -1649,7 +1699,9 @@
     </row>
     <row r="16" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="45"/>
-      <c r="B16" s="23"/>
+      <c r="B16" s="53" t="s">
+        <v>27</v>
+      </c>
       <c r="C16" s="24">
         <f>C14-C15</f>
         <v>3</v>
@@ -1701,7 +1753,9 @@
       <c r="A17" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="16"/>
+      <c r="B17" s="51" t="s">
+        <v>25</v>
+      </c>
       <c r="C17" s="16">
         <v>6</v>
       </c>
@@ -1736,7 +1790,9 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="44"/>
-      <c r="B18" s="21"/>
+      <c r="B18" s="52" t="s">
+        <v>26</v>
+      </c>
       <c r="C18" s="21">
         <v>1</v>
       </c>
@@ -1774,7 +1830,9 @@
     </row>
     <row r="19" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="45"/>
-      <c r="B19" s="23"/>
+      <c r="B19" s="53" t="s">
+        <v>27</v>
+      </c>
       <c r="C19" s="23">
         <f>C17-C18</f>
         <v>5</v>
@@ -1826,7 +1884,9 @@
       <c r="A20" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="16"/>
+      <c r="B20" s="51" t="s">
+        <v>25</v>
+      </c>
       <c r="C20" s="16">
         <v>5</v>
       </c>
@@ -1861,7 +1921,9 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="44"/>
-      <c r="B21" s="21"/>
+      <c r="B21" s="52" t="s">
+        <v>26</v>
+      </c>
       <c r="C21" s="21">
         <v>1</v>
       </c>
@@ -1899,7 +1961,9 @@
     </row>
     <row r="22" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="45"/>
-      <c r="B22" s="23"/>
+      <c r="B22" s="53" t="s">
+        <v>27</v>
+      </c>
       <c r="C22" s="23">
         <f>C20-C21</f>
         <v>4</v>
@@ -1949,7 +2013,9 @@
       <c r="A23" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="16"/>
+      <c r="B23" s="51" t="s">
+        <v>25</v>
+      </c>
       <c r="C23" s="16">
         <v>6</v>
       </c>
@@ -1984,7 +2050,9 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="44"/>
-      <c r="B24" s="21"/>
+      <c r="B24" s="52" t="s">
+        <v>26</v>
+      </c>
       <c r="C24" s="21">
         <v>3</v>
       </c>
@@ -2022,7 +2090,9 @@
     </row>
     <row r="25" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="45"/>
-      <c r="B25" s="23"/>
+      <c r="B25" s="53" t="s">
+        <v>27</v>
+      </c>
       <c r="C25" s="24">
         <f>C23-C24</f>
         <v>3</v>
@@ -2074,7 +2144,9 @@
       <c r="A26" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="16"/>
+      <c r="B26" s="51" t="s">
+        <v>25</v>
+      </c>
       <c r="C26" s="16">
         <v>8</v>
       </c>
@@ -2109,7 +2181,9 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="44"/>
-      <c r="B27" s="21"/>
+      <c r="B27" s="52" t="s">
+        <v>26</v>
+      </c>
       <c r="C27" s="21">
         <v>2</v>
       </c>
@@ -2147,7 +2221,9 @@
     </row>
     <row r="28" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="45"/>
-      <c r="B28" s="23"/>
+      <c r="B28" s="53" t="s">
+        <v>27</v>
+      </c>
       <c r="C28" s="23">
         <f>C26-C27</f>
         <v>6</v>
